--- a/Свод договоренностей.xlsx
+++ b/Свод договоренностей.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr date1904="0"/>
   <s:bookViews>
     <s:workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
@@ -2092,11 +2092,17 @@
 170206
 170207</s:t>
   </s:si>
+  <s:si>
+    <s:t>Дали общий ответ на жалобы на застройщика, фейком не считать:</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Дали общий ответ на жалобы на застройщика, фейком не считать: 549206 549234 549235 549250 549261 549253 549265 549268 549211 549326</s:t>
+  </s:si>
 </s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<s:styleSheet xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
+<s:styleSheet xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2">
   <s:numFmts count="2">
     <s:numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <s:numFmt numFmtId="165" formatCode="dd\.mm"/>
@@ -2736,7 +2742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <s:sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25"/>
   <s:cols>
     <s:col min="2" max="7" width="44.727" customWidth="1"/>
@@ -6285,7 +6291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <s:sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25"/>
   <s:cols>
     <s:col min="1" max="1" width="13.73" customWidth="1"/>
@@ -7384,6 +7390,17 @@
       </s:c>
       <s:c r="D106" t="s">
         <s:v>364</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="107" ht="29.25">
+      <s:c r="A107" s="25">
+        <s:v>46307</s:v>
+      </s:c>
+      <s:c r="B107" s="0" t="s">
+        <s:v>146</s:v>
+      </s:c>
+      <s:c r="C107" s="24" t="s">
+        <s:v>465</s:v>
       </s:c>
     </s:row>
   </s:sheetData>
@@ -7399,7 +7416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <s:sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25"/>
   <s:sheetData/>
   <s:printOptions headings="0" gridLines="0"/>
